--- a/Data/Regression Evidence 2025/Workday_NewHire_Spain_Regression_PK17.xlsx
+++ b/Data/Regression Evidence 2025/Workday_NewHire_Spain_Regression_PK17.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="121">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -208,16 +208,13 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10700263</t>
-  </si>
-  <si>
     <t>Passed</t>
   </si>
   <si>
     <t>356 Recruitment (Posob Zujefy Pyronu (2577) (Inherited))</t>
   </si>
   <si>
-    <t>FourteenJuly</t>
+    <t>FourAugust</t>
   </si>
   <si>
     <t>NEWHIRE</t>
@@ -319,7 +316,7 @@
     <t>ID Card (DNI) Number</t>
   </si>
   <si>
-    <t>10006628A</t>
+    <t>10006639A</t>
   </si>
   <si>
     <t>BBVAESMM111</t>
@@ -340,19 +337,22 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10700264</t>
+    <t>10700476</t>
   </si>
   <si>
     <t>365 Store Management (Cisuw Hapagu Pahame (10274587))</t>
   </si>
   <si>
-    <t>NEWHIREMANAGER</t>
+    <t>EightAugustNewManger</t>
+  </si>
+  <si>
+    <t>NewManger</t>
   </si>
   <si>
     <t>SLNameTwoo</t>
   </si>
   <si>
-    <t>Auto 62179809</t>
+    <t>Auto 39553277</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -377,7 +377,7 @@
 </t>
   </si>
   <si>
-    <t>10006629A</t>
+    <t>10006648A</t>
   </si>
   <si>
     <t>54 - ENSEÑANZAS UNIVERSITARIAS DE PRIMER CICLO Y EQUIVALENTES</t>
@@ -483,7 +483,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -509,7 +509,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -522,6 +523,11 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -555,7 +561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -649,6 +655,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -995,8 +1004,8 @@
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
     <col min="2" max="2" width="51.36328125" customWidth="1"/>
     <col min="3" max="3" width="10.1796875" customWidth="1"/>
-    <col min="4" max="4" width="41.453125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="4" max="4" width="54.7265625" customWidth="1"/>
+    <col min="5" max="5" width="32.26953125" customWidth="1"/>
     <col min="6" max="6" width="13.453125" customWidth="1"/>
     <col min="7" max="7" width="21.81640625" customWidth="1"/>
     <col min="8" max="8" width="13.453125" customWidth="1"/>
@@ -1271,219 +1280,219 @@
       <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="7">
+        <v>10700463</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>68</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>69</v>
       </c>
       <c r="I2" s="12">
         <v>919193394</v>
       </c>
       <c r="J2" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="K2" s="12" t="s">
         <v>70</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>71</v>
       </c>
       <c r="L2" s="13">
         <f t="shared" ref="L2" si="0">TODAY()-7</f>
-        <v>45845</v>
+        <v>45870</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O2" s="12">
         <v>44</v>
       </c>
       <c r="P2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q2" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="R2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="T2" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="R2" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="T2" s="16" t="s">
+      <c r="U2" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="U2" s="17" t="s">
-        <v>76</v>
-      </c>
       <c r="V2" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W2" s="18">
         <f t="shared" ref="W2" si="1">TODAY()-7</f>
-        <v>45845</v>
+        <v>45870</v>
       </c>
       <c r="X2" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y2" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="Y2" s="19" t="s">
+      <c r="Z2" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="Z2" s="20" t="s">
+      <c r="AA2" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="AB2" t="s">
         <v>80</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>81</v>
       </c>
       <c r="AC2" s="22">
         <v>356</v>
       </c>
       <c r="AD2" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE2" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AE2" s="14" t="s">
+      <c r="AF2" t="s">
         <v>83</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>84</v>
       </c>
       <c r="AG2" s="24">
         <f>TODAY()+365</f>
-        <v>46217</v>
+        <v>46242</v>
       </c>
       <c r="AH2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI2" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="AI2" s="25" t="s">
+      <c r="AJ2" t="s">
         <v>86</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="AK2" s="12" t="s">
+      <c r="AL2" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="AL2" s="16" t="s">
+      <c r="AM2" s="26" t="s">
         <v>89</v>
-      </c>
-      <c r="AM2" s="26" t="s">
-        <v>90</v>
       </c>
       <c r="AN2" s="26">
         <f t="shared" ref="AN2" si="2">TODAY()+7</f>
-        <v>45859</v>
+        <v>45884</v>
       </c>
       <c r="AO2" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP2" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="AP2" s="15" t="s">
+      <c r="AQ2" s="16" t="s">
         <v>92</v>
-      </c>
-      <c r="AQ2" s="16" t="s">
-        <v>93</v>
       </c>
       <c r="AR2" s="24">
         <f t="shared" ref="AR2" si="3">TODAY()+365</f>
-        <v>46217</v>
+        <v>46242</v>
       </c>
       <c r="AS2" s="27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AT2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AU2" s="13">
         <v>29221</v>
       </c>
       <c r="AV2" s="28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AW2" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AX2" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY2" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="AX2" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY2" s="28" t="s">
+      <c r="AZ2" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="AZ2" s="29" t="s">
+      <c r="BA2" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="BB2" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="BC2" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="BA2" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="BB2" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC2" s="30" t="s">
+      <c r="BD2" s="31">
+        <v>281000758119</v>
+      </c>
+      <c r="BE2" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="BF2" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="BD2" s="31">
-        <v>281000758106</v>
-      </c>
-      <c r="BE2" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="BF2" s="30" t="s">
+      <c r="BG2" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="BG2" s="32" t="s">
+      <c r="BH2" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="BH2" s="30" t="s">
+      <c r="BI2" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="BI2" s="30" t="s">
+      <c r="BJ2" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="BJ2" s="30" t="s">
+      <c r="BK2" s="30" t="s">
         <v>103</v>
-      </c>
-      <c r="BK2" s="30" t="s">
-        <v>104</v>
       </c>
       <c r="BL2" s="30">
         <v>36526</v>
       </c>
       <c r="BM2" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="C3" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>108</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>66</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>109</v>
@@ -1492,25 +1501,25 @@
         <v>110</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I3" s="12">
         <v>919193436</v>
       </c>
       <c r="J3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="12" t="s">
         <v>70</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>71</v>
       </c>
       <c r="L3" s="13">
         <v>45800</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O3" s="12">
         <v>44</v>
@@ -1519,28 +1528,28 @@
         <v>28013</v>
       </c>
       <c r="Q3" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="T3" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="R3" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="S3" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="T3" s="16" t="s">
+      <c r="U3" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="U3" s="15" t="s">
-        <v>76</v>
-      </c>
       <c r="V3" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W3" s="18">
         <v>45800</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y3" s="19" t="s">
         <v>111</v>
@@ -1561,16 +1570,16 @@
         <v>100</v>
       </c>
       <c r="AE3" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF3" t="s">
         <v>115</v>
       </c>
-      <c r="AG3" s="35" t="s">
-        <v>78</v>
+      <c r="AG3" s="36" t="s">
+        <v>77</v>
       </c>
       <c r="AH3" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI3" s="25" t="s">
         <v>116</v>
@@ -1579,82 +1588,82 @@
         <v>117</v>
       </c>
       <c r="AK3" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="AL3" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="AL3" s="37" t="s">
         <v>118</v>
       </c>
       <c r="AM3" s="26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AN3" s="26">
         <v>45814</v>
       </c>
       <c r="AO3" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP3" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="AP3" s="15" t="s">
+      <c r="AQ3" s="16" t="s">
         <v>92</v>
-      </c>
-      <c r="AQ3" s="16" t="s">
-        <v>93</v>
       </c>
       <c r="AR3" s="24">
         <v>46172</v>
       </c>
       <c r="AS3" s="27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AT3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AU3" s="13">
         <v>29221</v>
       </c>
       <c r="AV3" s="28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AW3" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AX3" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY3" s="28" t="s">
         <v>95</v>
-      </c>
-      <c r="AX3" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY3" s="28" t="s">
-        <v>96</v>
       </c>
       <c r="AZ3" s="29">
         <v>40844</v>
       </c>
       <c r="BA3" s="28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="BB3" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="BC3" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="BD3" s="31">
+        <v>281000758128</v>
+      </c>
+      <c r="BE3" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="BF3" s="30" t="s">
         <v>98</v>
-      </c>
-      <c r="BD3" s="31">
-        <v>281000758107</v>
-      </c>
-      <c r="BE3" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="BF3" s="30" t="s">
-        <v>99</v>
       </c>
       <c r="BG3" s="32" t="s">
         <v>119</v>
       </c>
       <c r="BH3" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="BI3" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="BI3" s="30" t="s">
+      <c r="BJ3" s="30" t="s">
         <v>102</v>
-      </c>
-      <c r="BJ3" s="30" t="s">
-        <v>103</v>
       </c>
       <c r="BK3" s="30" t="s">
         <v>120</v>
@@ -1663,16 +1672,16 @@
         <v>36526</v>
       </c>
       <c r="BM3" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="8"/>
+      <c r="C4" s="33"/>
       <c r="D4" s="9"/>
       <c r="E4" s="10"/>
-      <c r="F4" s="37"/>
+      <c r="F4" s="38"/>
       <c r="G4" s="10"/>
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
@@ -1695,7 +1704,7 @@
       <c r="AA4" s="21"/>
       <c r="AC4" s="22"/>
       <c r="AE4" s="14"/>
-      <c r="AG4" s="35"/>
+      <c r="AG4" s="36"/>
       <c r="AH4" s="12"/>
       <c r="AI4" s="25"/>
       <c r="AK4" s="12"/>
@@ -1730,10 +1739,10 @@
     <row r="5" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33"/>
       <c r="B5" s="33"/>
-      <c r="C5" s="8"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="37"/>
+      <c r="F5" s="38"/>
       <c r="G5" s="10"/>
       <c r="H5" s="11"/>
       <c r="I5" s="12"/>
@@ -1757,7 +1766,7 @@
       <c r="AC5" s="22"/>
       <c r="AD5" s="23"/>
       <c r="AE5" s="14"/>
-      <c r="AG5" s="35"/>
+      <c r="AG5" s="36"/>
       <c r="AH5" s="12"/>
       <c r="AI5" s="25"/>
       <c r="AK5" s="12"/>
@@ -1792,10 +1801,10 @@
     <row r="6" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33"/>
       <c r="B6" s="33"/>
-      <c r="C6" s="8"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
-      <c r="F6" s="37"/>
+      <c r="F6" s="38"/>
       <c r="G6" s="10"/>
       <c r="H6" s="11"/>
       <c r="I6" s="12"/>
@@ -1854,10 +1863,10 @@
     <row r="7" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33"/>
       <c r="B7" s="33"/>
-      <c r="C7" s="8"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="9"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="37"/>
+      <c r="F7" s="38"/>
       <c r="G7" s="10"/>
       <c r="H7" s="11"/>
       <c r="I7" s="12"/>
@@ -1880,7 +1889,7 @@
       <c r="AA7" s="21"/>
       <c r="AC7" s="22"/>
       <c r="AE7" s="14"/>
-      <c r="AG7" s="35"/>
+      <c r="AG7" s="36"/>
       <c r="AH7" s="12"/>
       <c r="AI7" s="25"/>
       <c r="AK7" s="12"/>
@@ -1915,10 +1924,10 @@
     <row r="8" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33"/>
       <c r="B8" s="33"/>
-      <c r="C8" s="8"/>
+      <c r="C8" s="33"/>
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
-      <c r="F8" s="37"/>
+      <c r="F8" s="38"/>
       <c r="G8" s="10"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
@@ -1941,7 +1950,7 @@
       <c r="AA8" s="21"/>
       <c r="AC8" s="22"/>
       <c r="AE8" s="14"/>
-      <c r="AG8" s="35"/>
+      <c r="AG8" s="36"/>
       <c r="AH8" s="12"/>
       <c r="AI8" s="25"/>
       <c r="AK8" s="12"/>
@@ -1976,10 +1985,10 @@
     <row r="9" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33"/>
       <c r="B9" s="33"/>
-      <c r="C9" s="8"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="37"/>
+      <c r="F9" s="38"/>
       <c r="G9" s="10"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
@@ -2038,10 +2047,10 @@
     <row r="10" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33"/>
       <c r="B10" s="33"/>
-      <c r="C10" s="8"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
-      <c r="F10" s="37"/>
+      <c r="F10" s="38"/>
       <c r="G10" s="10"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
@@ -2061,10 +2070,10 @@
       <c r="W10" s="18"/>
       <c r="X10" s="12"/>
       <c r="Y10" s="19"/>
-      <c r="AA10" s="38"/>
+      <c r="AA10" s="39"/>
       <c r="AC10" s="22"/>
       <c r="AE10" s="14"/>
-      <c r="AG10" s="35"/>
+      <c r="AG10" s="36"/>
       <c r="AH10" s="12"/>
       <c r="AI10" s="25"/>
       <c r="AK10" s="12"/>
@@ -2099,10 +2108,10 @@
     <row r="11" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33"/>
       <c r="B11" s="33"/>
-      <c r="C11" s="8"/>
+      <c r="C11" s="33"/>
       <c r="D11" s="9"/>
       <c r="E11" s="10"/>
-      <c r="F11" s="37"/>
+      <c r="F11" s="38"/>
       <c r="G11" s="10"/>
       <c r="H11" s="11"/>
       <c r="I11" s="12"/>
@@ -2125,7 +2134,7 @@
       <c r="AA11" s="21"/>
       <c r="AC11" s="22"/>
       <c r="AE11" s="14"/>
-      <c r="AG11" s="35"/>
+      <c r="AG11" s="36"/>
       <c r="AH11" s="12"/>
       <c r="AI11" s="25"/>
       <c r="AK11" s="12"/>
@@ -2160,10 +2169,10 @@
     <row r="12" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33"/>
       <c r="B12" s="33"/>
-      <c r="C12" s="8"/>
+      <c r="C12" s="33"/>
       <c r="D12" s="9"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="37"/>
+      <c r="F12" s="38"/>
       <c r="G12" s="10"/>
       <c r="H12" s="11"/>
       <c r="I12" s="12"/>
@@ -2183,7 +2192,7 @@
       <c r="W12" s="18"/>
       <c r="X12" s="12"/>
       <c r="Y12" s="19"/>
-      <c r="Z12" s="39"/>
+      <c r="Z12" s="40"/>
       <c r="AA12" s="21"/>
       <c r="AC12" s="22"/>
       <c r="AE12" s="14"/>
@@ -2222,10 +2231,10 @@
     <row r="13" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33"/>
       <c r="B13" s="33"/>
-      <c r="C13" s="8"/>
+      <c r="C13" s="33"/>
       <c r="D13" s="9"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="37"/>
+      <c r="F13" s="38"/>
       <c r="G13" s="10"/>
       <c r="H13" s="11"/>
       <c r="I13" s="12"/>
@@ -2245,12 +2254,12 @@
       <c r="W13" s="18"/>
       <c r="X13" s="12"/>
       <c r="Y13" s="19"/>
-      <c r="Z13" s="39"/>
+      <c r="Z13" s="40"/>
       <c r="AA13" s="21"/>
-      <c r="AB13" s="39"/>
+      <c r="AB13" s="40"/>
       <c r="AC13" s="22"/>
       <c r="AE13" s="14"/>
-      <c r="AG13" s="35"/>
+      <c r="AG13" s="36"/>
       <c r="AH13" s="12"/>
       <c r="AI13" s="25"/>
       <c r="AK13" s="12"/>
@@ -2285,66 +2294,66 @@
     <row r="14" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33"/>
       <c r="B14" s="33"/>
-      <c r="C14" s="8"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="37"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="38"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
       <c r="L14" s="18"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="44"/>
-      <c r="O14" s="42"/>
+      <c r="M14" s="44"/>
+      <c r="N14" s="45"/>
+      <c r="O14" s="43"/>
       <c r="P14" s="12"/>
-      <c r="Q14" s="44"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="45"/>
-      <c r="U14" s="46"/>
-      <c r="V14" s="42"/>
+      <c r="Q14" s="45"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="47"/>
+      <c r="V14" s="43"/>
       <c r="W14" s="18"/>
-      <c r="X14" s="42"/>
-      <c r="Y14" s="47"/>
-      <c r="Z14" s="35"/>
-      <c r="AA14" s="48"/>
-      <c r="AB14" s="35"/>
-      <c r="AC14" s="49"/>
-      <c r="AD14" s="35"/>
-      <c r="AE14" s="43"/>
-      <c r="AF14" s="35"/>
-      <c r="AG14" s="35"/>
-      <c r="AH14" s="42"/>
+      <c r="X14" s="43"/>
+      <c r="Y14" s="48"/>
+      <c r="Z14" s="36"/>
+      <c r="AA14" s="49"/>
+      <c r="AB14" s="36"/>
+      <c r="AC14" s="50"/>
+      <c r="AD14" s="36"/>
+      <c r="AE14" s="44"/>
+      <c r="AF14" s="36"/>
+      <c r="AG14" s="36"/>
+      <c r="AH14" s="43"/>
       <c r="AI14" s="25"/>
-      <c r="AJ14" s="50"/>
-      <c r="AK14" s="42"/>
-      <c r="AL14" s="45"/>
-      <c r="AM14" s="51"/>
-      <c r="AN14" s="51"/>
+      <c r="AJ14" s="51"/>
+      <c r="AK14" s="43"/>
+      <c r="AL14" s="46"/>
+      <c r="AM14" s="52"/>
+      <c r="AN14" s="52"/>
       <c r="AO14" s="14"/>
       <c r="AP14" s="15"/>
       <c r="AQ14" s="16"/>
       <c r="AR14" s="24"/>
-      <c r="AS14" s="52"/>
-      <c r="AT14" s="35"/>
+      <c r="AS14" s="53"/>
+      <c r="AT14" s="36"/>
       <c r="AU14" s="18"/>
-      <c r="AV14" s="53"/>
-      <c r="AW14" s="53"/>
-      <c r="AX14" s="53"/>
-      <c r="AY14" s="53"/>
-      <c r="AZ14" s="54"/>
-      <c r="BA14" s="53"/>
-      <c r="BB14" s="55"/>
-      <c r="BC14" s="55"/>
+      <c r="AV14" s="54"/>
+      <c r="AW14" s="54"/>
+      <c r="AX14" s="54"/>
+      <c r="AY14" s="54"/>
+      <c r="AZ14" s="55"/>
+      <c r="BA14" s="54"/>
+      <c r="BB14" s="56"/>
+      <c r="BC14" s="56"/>
       <c r="BD14" s="31"/>
-      <c r="BE14" s="55"/>
-      <c r="BF14" s="55"/>
+      <c r="BE14" s="56"/>
+      <c r="BF14" s="56"/>
       <c r="BG14" s="32"/>
-      <c r="BH14" s="55"/>
-      <c r="BI14" s="55"/>
-      <c r="BJ14" s="55"/>
+      <c r="BH14" s="56"/>
+      <c r="BI14" s="56"/>
+      <c r="BJ14" s="56"/>
       <c r="BK14" s="30"/>
       <c r="BL14" s="30"/>
       <c r="BM14" s="30"/>
@@ -2352,10 +2361,10 @@
     <row r="15" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
       <c r="B15" s="33"/>
-      <c r="C15" s="8"/>
+      <c r="C15" s="33"/>
       <c r="D15" s="9"/>
       <c r="E15" s="10"/>
-      <c r="F15" s="37"/>
+      <c r="F15" s="38"/>
       <c r="G15" s="10"/>
       <c r="H15" s="11"/>
       <c r="I15" s="12"/>
@@ -2414,10 +2423,10 @@
     <row r="16" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33"/>
       <c r="B16" s="33"/>
-      <c r="C16" s="8"/>
+      <c r="C16" s="33"/>
       <c r="D16" s="9"/>
       <c r="E16" s="10"/>
-      <c r="F16" s="37"/>
+      <c r="F16" s="38"/>
       <c r="G16" s="10"/>
       <c r="H16" s="11"/>
       <c r="I16" s="12"/>
@@ -2437,11 +2446,11 @@
       <c r="W16" s="18"/>
       <c r="X16" s="12"/>
       <c r="Y16" s="19"/>
-      <c r="Z16" s="39"/>
+      <c r="Z16" s="40"/>
       <c r="AA16" s="21"/>
       <c r="AC16" s="22"/>
       <c r="AE16" s="14"/>
-      <c r="AG16" s="35"/>
+      <c r="AG16" s="36"/>
       <c r="AH16" s="12"/>
       <c r="AI16" s="25"/>
       <c r="AK16" s="12"/>
@@ -2475,7 +2484,7 @@
     </row>
     <row r="17" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2555,7 +2564,7 @@
       <c r="BY19" s="2"/>
       <c r="BZ19" s="2"/>
     </row>
-    <row r="20" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2635,7 +2644,7 @@
       <c r="BY20" s="2"/>
       <c r="BZ20" s="2"/>
     </row>
-    <row r="21" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2715,7 +2724,7 @@
       <c r="BY21" s="2"/>
       <c r="BZ21" s="2"/>
     </row>
-    <row r="22" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2795,7 +2804,7 @@
       <c r="BY22" s="2"/>
       <c r="BZ22" s="2"/>
     </row>
-    <row r="23" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2875,7 +2884,7 @@
       <c r="BY23" s="2"/>
       <c r="BZ23" s="2"/>
     </row>
-    <row r="24" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2955,7 +2964,7 @@
       <c r="BY24" s="2"/>
       <c r="BZ24" s="2"/>
     </row>
-    <row r="25" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3035,7 +3044,7 @@
       <c r="BY25" s="2"/>
       <c r="BZ25" s="2"/>
     </row>
-    <row r="26" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3115,7 +3124,7 @@
       <c r="BY26" s="2"/>
       <c r="BZ26" s="2"/>
     </row>
-    <row r="27" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3195,7 +3204,7 @@
       <c r="BY27" s="2"/>
       <c r="BZ27" s="2"/>
     </row>
-    <row r="28" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3275,7 +3284,7 @@
       <c r="BY28" s="2"/>
       <c r="BZ28" s="2"/>
     </row>
-    <row r="29" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3355,7 +3364,7 @@
       <c r="BY29" s="2"/>
       <c r="BZ29" s="2"/>
     </row>
-    <row r="30" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3435,7 +3444,7 @@
       <c r="BY30" s="2"/>
       <c r="BZ30" s="2"/>
     </row>
-    <row r="31" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3515,7 +3524,7 @@
       <c r="BY31" s="2"/>
       <c r="BZ31" s="2"/>
     </row>
-    <row r="32" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3595,7 +3604,7 @@
       <c r="BY32" s="2"/>
       <c r="BZ32" s="2"/>
     </row>
-    <row r="33" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -3675,7 +3684,7 @@
       <c r="BY33" s="2"/>
       <c r="BZ33" s="2"/>
     </row>
-    <row r="34" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -3755,7 +3764,7 @@
       <c r="BY34" s="2"/>
       <c r="BZ34" s="2"/>
     </row>
-    <row r="35" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3835,7 +3844,7 @@
       <c r="BY35" s="2"/>
       <c r="BZ35" s="2"/>
     </row>
-    <row r="36" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3915,7 +3924,7 @@
       <c r="BY36" s="2"/>
       <c r="BZ36" s="2"/>
     </row>
-    <row r="37" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -3995,7 +4004,7 @@
       <c r="BY37" s="2"/>
       <c r="BZ37" s="2"/>
     </row>
-    <row r="38" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4075,7 +4084,7 @@
       <c r="BY38" s="2"/>
       <c r="BZ38" s="2"/>
     </row>
-    <row r="39" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -4155,7 +4164,7 @@
       <c r="BY39" s="2"/>
       <c r="BZ39" s="2"/>
     </row>
-    <row r="40" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4235,7 +4244,7 @@
       <c r="BY40" s="2"/>
       <c r="BZ40" s="2"/>
     </row>
-    <row r="41" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -4315,7 +4324,7 @@
       <c r="BY41" s="2"/>
       <c r="BZ41" s="2"/>
     </row>
-    <row r="42" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -4395,7 +4404,7 @@
       <c r="BY42" s="2"/>
       <c r="BZ42" s="2"/>
     </row>
-    <row r="43" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -4475,7 +4484,7 @@
       <c r="BY43" s="2"/>
       <c r="BZ43" s="2"/>
     </row>
-    <row r="44" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -4555,7 +4564,7 @@
       <c r="BY44" s="2"/>
       <c r="BZ44" s="2"/>
     </row>
-    <row r="45" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -4635,7 +4644,7 @@
       <c r="BY45" s="2"/>
       <c r="BZ45" s="2"/>
     </row>
-    <row r="46" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4715,7 +4724,7 @@
       <c r="BY46" s="2"/>
       <c r="BZ46" s="2"/>
     </row>
-    <row r="47" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -4795,7 +4804,7 @@
       <c r="BY47" s="2"/>
       <c r="BZ47" s="2"/>
     </row>
-    <row r="48" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -4875,7 +4884,7 @@
       <c r="BY48" s="2"/>
       <c r="BZ48" s="2"/>
     </row>
-    <row r="49" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -4955,7 +4964,7 @@
       <c r="BY49" s="2"/>
       <c r="BZ49" s="2"/>
     </row>
-    <row r="50" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -5035,7 +5044,7 @@
       <c r="BY50" s="2"/>
       <c r="BZ50" s="2"/>
     </row>
-    <row r="51" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -5115,7 +5124,7 @@
       <c r="BY51" s="2"/>
       <c r="BZ51" s="2"/>
     </row>
-    <row r="52" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -5195,7 +5204,7 @@
       <c r="BY52" s="2"/>
       <c r="BZ52" s="2"/>
     </row>
-    <row r="53" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
